--- a/InputData/io-model/BECbIC/cn-BAU Employee Compensation by ISIC Code.xlsx
+++ b/InputData/io-model/BECbIC/cn-BAU Employee Compensation by ISIC Code.xlsx
@@ -1,22 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12540"/>
+    <workbookView windowWidth="28800" windowHeight="12300" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="2020年全国投入产出表" sheetId="2" r:id="rId2"/>
+    <sheet name="2020 National eps IO" sheetId="2" r:id="rId2"/>
     <sheet name="BECbIC" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525" iterate="1" iterateCount="100" iterateDelta="1e-5"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="141">
   <si>
     <t>BECbIC BAU Employee Compensation by ISIC Code</t>
   </si>
@@ -24,30 +37,132 @@
     <t>Source:</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>020 National Input-outout Table</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BS</t>
+    </r>
+  </si>
+  <si>
+    <t>https://data.stats.gov.cn/files/html/quickSearch/trcc/trcc01.html</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>The "2020 National Input-output Table" is a summary of the input-output table of 42 departments based on the competitive and non-competitive tables in the annual input-output table of China in 2020 and the EPS model of the United States. Government consumption expenditure is based on the amount of government consumption expenditure by industry in the "2020 National input-output Table" multiplied by the exchange rate of the RMB in 2020 against the US dollar in 2012.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Employee compensation can be obtained directly through the exchange rate in the "20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">20 national </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>input-output table".</t>
+    </r>
+  </si>
+  <si>
+    <t>Currency Conversion</t>
+  </si>
+  <si>
+    <t>We convert 2020 RMB to 2012 USD with the following conversion factor:</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>020</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> RMB / 2012 USD</t>
+    </r>
+  </si>
+  <si>
     <t>2020年全国投入产出表</t>
   </si>
   <si>
-    <t>国家统计局</t>
-  </si>
-  <si>
-    <t>https://data.stats.gov.cn/files/html/quickSearch/trcc/trcc01.html</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>“2020年全国投入产出表”是根据我国2020年全年投入产出表中竞争型和非竞争型两张表结合美国EPS模型总结出来42个部门的投入产出表。政府消费支出是根据“2020年全国投入产出表”中各行业政府消费支出数额乘以当年2020年人民币相对2012美元的汇率得出。</t>
-  </si>
-  <si>
-    <t>劳动者报酬在“2020年全国投入产出表”中可以直接通过汇率求得。</t>
-  </si>
-  <si>
-    <t>We convert 2020 RMB to 2012 USD with the following conversion factor:</t>
-  </si>
-  <si>
-    <t>当年人民币相对2012美元</t>
-  </si>
-  <si>
     <t>(按当年生产者价格计算） （Data are calculated at producers' prices in 2020)</t>
   </si>
   <si>
@@ -270,24 +385,24 @@
     <t>ISIC 22</t>
   </si>
   <si>
+    <t>ISIC 239</t>
+  </si>
+  <si>
+    <t>ISIC 241</t>
+  </si>
+  <si>
+    <t>ISIC 242</t>
+  </si>
+  <si>
+    <t>ISIC 25</t>
+  </si>
+  <si>
+    <t>ISIC 28</t>
+  </si>
+  <si>
     <t>ISIC 231</t>
   </si>
   <si>
-    <t>ISIC 241</t>
-  </si>
-  <si>
-    <t>ISIC 242</t>
-  </si>
-  <si>
-    <t>ISIC 25</t>
-  </si>
-  <si>
-    <t>ISIC 28</t>
-  </si>
-  <si>
-    <t>ISIC 239</t>
-  </si>
-  <si>
     <t>ISIC 29</t>
   </si>
   <si>
@@ -336,6 +451,9 @@
     <t>ISIC 61</t>
   </si>
   <si>
+    <t>ISIC 62T63</t>
+  </si>
+  <si>
     <t>ISIC 69T82</t>
   </si>
   <si>
@@ -427,9 +545,6 @@
   </si>
   <si>
     <t>Unit: dimensionless (%)</t>
-  </si>
-  <si>
-    <t>ISIC 62T63</t>
   </si>
   <si>
     <t>Employee Compensation</t>
@@ -438,7 +553,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -446,7 +561,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0000_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -463,12 +578,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -489,6 +606,11 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -541,39 +663,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -582,14 +676,6 @@
       <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -629,6 +715,21 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -679,7 +780,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -699,55 +821,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -765,31 +845,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -813,6 +881,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -825,7 +905,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -849,7 +953,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -868,6 +984,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -909,30 +1031,6 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top/>
       <bottom style="medium">
@@ -1026,6 +1124,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -1078,6 +1187,19 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1146,21 +1268,6 @@
         <color auto="1"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1193,6 +1300,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1247,434 +1369,422 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="53">
+  <cellStyleXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="51"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="51" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="51"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="51" applyFill="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="51" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="51" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="51" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="51" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="51" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="52" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="51" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="15" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="16" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="15" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="52" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="20" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="51" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="51" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="51" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="51" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="51" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="51" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="16" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="46" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="51" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="20" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="51" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="51" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="51" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="51" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="51" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="53">
+  <cellStyles count="54">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="常规_Sheet1_1 2" xfId="46"/>
-    <cellStyle name="强调文字颜色 6" xfId="47" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="48" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="49" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="50"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 4" xfId="50"/>
     <cellStyle name="常规 5" xfId="51"/>
-    <cellStyle name="常规 4" xfId="52"/>
+    <cellStyle name="常规_Sheet1_1 2" xfId="52"/>
+    <cellStyle name="常规 3 2" xfId="53"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -1952,115 +2062,103 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E36"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:E34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="77.5666666666667" style="3" customWidth="1"/>
+    <col min="2" max="2" width="77.6296296296296" style="3" customWidth="1"/>
     <col min="3" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="1" spans="1:1">
-      <c r="A1" s="78" t="s">
+    <row r="1" spans="1:1">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="3" customFormat="1" spans="1:5">
-      <c r="A3" s="79" t="s">
+    <row r="3" spans="1:5">
+      <c r="A3" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="80" t="s">
+      <c r="B3" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="79"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="79"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
     </row>
-    <row r="4" s="3" customFormat="1" spans="1:5">
-      <c r="A4" s="81"/>
-      <c r="B4" s="81" t="s">
+    <row r="4" spans="2:2">
+      <c r="B4" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="81"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
     </row>
-    <row r="5" s="3" customFormat="1" spans="1:5">
-      <c r="A5" s="81"/>
-      <c r="B5" s="82">
+    <row r="5" spans="2:4">
+      <c r="B5" s="72">
         <v>2020</v>
       </c>
-      <c r="C5" s="81"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="81"/>
+      <c r="D5" s="72"/>
     </row>
-    <row r="6" s="3" customFormat="1" spans="1:5">
-      <c r="A6" s="81"/>
-      <c r="B6" s="81" t="s">
+    <row r="6" spans="2:2">
+      <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="81"/>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
     </row>
-    <row r="7" s="3" customFormat="1" spans="2:2">
-      <c r="B7" s="83"/>
+    <row r="7" spans="2:2">
+      <c r="B7" s="73"/>
     </row>
-    <row r="8" s="3" customFormat="1" spans="1:1">
-      <c r="A8" s="78" t="s">
+    <row r="8" spans="1:2">
+      <c r="A8" s="70" t="s">
         <v>5</v>
       </c>
+      <c r="B8" s="3" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="3" t="s">
-        <v>6</v>
+    <row r="9" spans="2:2">
+      <c r="B9" s="74" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="10" s="3" customFormat="1" spans="1:2">
-      <c r="A10" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="80"/>
+    <row r="11" spans="1:1">
+      <c r="A11" s="70" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="12" s="3" customFormat="1" spans="2:2">
-      <c r="B12" s="84"/>
+    <row r="12" spans="1:1">
+      <c r="A12" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="14" s="3" customFormat="1" spans="2:2">
-      <c r="B14" s="83"/>
+    <row r="13" spans="1:2">
+      <c r="A13" s="75">
+        <v>0.137650677988234</v>
+      </c>
+      <c r="B13" s="74" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="18" s="3" customFormat="1" spans="2:2">
-      <c r="B18" s="84"/>
+    <row r="15" spans="2:2">
+      <c r="B15" s="73"/>
     </row>
-    <row r="20" s="3" customFormat="1" spans="2:2">
-      <c r="B20" s="83"/>
+    <row r="19" spans="2:2">
+      <c r="B19" s="72"/>
     </row>
-    <row r="21" s="3" customFormat="1" spans="2:2">
-      <c r="B21" s="85"/>
+    <row r="21" spans="2:2">
+      <c r="B21" s="73"/>
     </row>
-    <row r="22" s="3" customFormat="1" spans="2:2">
-      <c r="B22" s="85"/>
+    <row r="22" spans="2:2">
+      <c r="B22" s="76"/>
     </row>
-    <row r="23" s="3" customFormat="1" spans="2:2">
-      <c r="B23" s="85"/>
+    <row r="23" spans="2:2">
+      <c r="B23" s="76"/>
     </row>
-    <row r="25" s="3" customFormat="1" spans="1:1">
-      <c r="A25" s="78"/>
+    <row r="24" spans="2:2">
+      <c r="B24" s="76"/>
     </row>
-    <row r="33" s="3" customFormat="1" spans="1:1">
-      <c r="A33" s="83"/>
+    <row r="26" spans="1:1">
+      <c r="A26" s="70"/>
     </row>
-    <row r="35" s="3" customFormat="1" spans="1:1">
-      <c r="A35" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" s="3" customFormat="1" spans="1:2">
-      <c r="A36" s="86">
-        <v>0.137650677988234</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>9</v>
-      </c>
+    <row r="34" spans="1:1">
+      <c r="A34" s="73"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2072,1355 +2170,1355 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BF11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:58">
-      <c r="A1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-      <c r="V1" s="8"/>
-      <c r="W1" s="8"/>
-      <c r="X1" s="8"/>
-      <c r="Y1" s="8"/>
-      <c r="Z1" s="8"/>
-      <c r="AA1" s="8"/>
-      <c r="AB1" s="8"/>
-      <c r="AC1" s="8"/>
-      <c r="AD1" s="8"/>
-      <c r="AE1" s="8"/>
-      <c r="AF1" s="8"/>
-      <c r="AG1" s="8"/>
-      <c r="AH1" s="8"/>
-      <c r="AI1" s="8"/>
-      <c r="AJ1" s="8"/>
-      <c r="AK1" s="8"/>
-      <c r="AL1" s="8"/>
-      <c r="AM1" s="8"/>
-      <c r="AN1" s="8"/>
-      <c r="AO1" s="8"/>
-      <c r="AP1" s="8"/>
-      <c r="AQ1" s="8"/>
-      <c r="AR1" s="8"/>
-      <c r="AS1" s="8"/>
-      <c r="AT1" s="8"/>
-      <c r="AU1" s="8"/>
-      <c r="AV1" s="8"/>
-      <c r="AW1" s="55"/>
-      <c r="AX1" s="8"/>
-      <c r="AY1" s="55"/>
-      <c r="AZ1" s="8"/>
-      <c r="BA1" s="8"/>
-      <c r="BB1" s="55"/>
-      <c r="BC1" s="8"/>
-      <c r="BD1" s="56"/>
-      <c r="BE1" s="8"/>
-      <c r="BF1" s="8"/>
+      <c r="A1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
+      <c r="Z1" s="5"/>
+      <c r="AA1" s="5"/>
+      <c r="AB1" s="5"/>
+      <c r="AC1" s="5"/>
+      <c r="AD1" s="5"/>
+      <c r="AE1" s="5"/>
+      <c r="AF1" s="5"/>
+      <c r="AG1" s="5"/>
+      <c r="AH1" s="5"/>
+      <c r="AI1" s="5"/>
+      <c r="AJ1" s="5"/>
+      <c r="AK1" s="5"/>
+      <c r="AL1" s="5"/>
+      <c r="AM1" s="5"/>
+      <c r="AN1" s="5"/>
+      <c r="AO1" s="5"/>
+      <c r="AP1" s="5"/>
+      <c r="AQ1" s="5"/>
+      <c r="AR1" s="5"/>
+      <c r="AS1" s="5"/>
+      <c r="AT1" s="5"/>
+      <c r="AU1" s="5"/>
+      <c r="AV1" s="5"/>
+      <c r="AW1" s="47"/>
+      <c r="AX1" s="5"/>
+      <c r="AY1" s="47"/>
+      <c r="AZ1" s="5"/>
+      <c r="BA1" s="5"/>
+      <c r="BB1" s="47"/>
+      <c r="BC1" s="5"/>
+      <c r="BD1" s="48"/>
+      <c r="BE1" s="5"/>
+      <c r="BF1" s="5"/>
     </row>
     <row r="2" spans="1:58">
-      <c r="A2" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11"/>
-      <c r="V2" s="11"/>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="11"/>
-      <c r="Z2" s="11"/>
-      <c r="AA2" s="11"/>
-      <c r="AB2" s="11"/>
-      <c r="AC2" s="11"/>
-      <c r="AD2" s="11"/>
-      <c r="AE2" s="11"/>
-      <c r="AF2" s="11"/>
-      <c r="AG2" s="11"/>
-      <c r="AH2" s="11"/>
-      <c r="AI2" s="11"/>
-      <c r="AJ2" s="11"/>
-      <c r="AK2" s="11"/>
-      <c r="AL2" s="11"/>
-      <c r="AM2" s="11"/>
-      <c r="AN2" s="11"/>
-      <c r="AO2" s="11"/>
-      <c r="AP2" s="11"/>
-      <c r="AQ2" s="11"/>
-      <c r="AR2" s="11"/>
-      <c r="AS2" s="41"/>
-      <c r="AT2" s="41"/>
-      <c r="AU2" s="42"/>
-      <c r="AV2" s="42"/>
-      <c r="AW2" s="57"/>
-      <c r="AX2" s="42"/>
-      <c r="AY2" s="57"/>
-      <c r="AZ2" s="42"/>
-      <c r="BA2" s="42"/>
-      <c r="BB2" s="57"/>
-      <c r="BC2" s="58"/>
-      <c r="BD2" s="56"/>
-      <c r="BE2" s="58"/>
-      <c r="BF2" s="8"/>
+      <c r="A2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
+      <c r="W2" s="7"/>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="7"/>
+      <c r="AA2" s="7"/>
+      <c r="AB2" s="7"/>
+      <c r="AC2" s="7"/>
+      <c r="AD2" s="7"/>
+      <c r="AE2" s="7"/>
+      <c r="AF2" s="7"/>
+      <c r="AG2" s="7"/>
+      <c r="AH2" s="7"/>
+      <c r="AI2" s="7"/>
+      <c r="AJ2" s="7"/>
+      <c r="AK2" s="7"/>
+      <c r="AL2" s="7"/>
+      <c r="AM2" s="7"/>
+      <c r="AN2" s="7"/>
+      <c r="AO2" s="7"/>
+      <c r="AP2" s="7"/>
+      <c r="AQ2" s="7"/>
+      <c r="AR2" s="7"/>
+      <c r="AS2" s="5"/>
+      <c r="AT2" s="5"/>
+      <c r="AU2" s="7"/>
+      <c r="AV2" s="7"/>
+      <c r="AW2" s="49"/>
+      <c r="AX2" s="7"/>
+      <c r="AY2" s="49"/>
+      <c r="AZ2" s="7"/>
+      <c r="BA2" s="7"/>
+      <c r="BB2" s="49"/>
+      <c r="BC2" s="50"/>
+      <c r="BD2" s="48"/>
+      <c r="BE2" s="50"/>
+      <c r="BF2" s="5"/>
     </row>
-    <row r="3" ht="14.25" spans="1:58">
-      <c r="A3" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
-      <c r="P3" s="15"/>
-      <c r="Q3" s="15"/>
-      <c r="R3" s="15"/>
-      <c r="S3" s="15"/>
-      <c r="T3" s="15"/>
-      <c r="U3" s="15"/>
-      <c r="V3" s="15"/>
-      <c r="W3" s="15"/>
-      <c r="X3" s="15"/>
-      <c r="Y3" s="15"/>
-      <c r="Z3" s="15"/>
-      <c r="AA3" s="15"/>
-      <c r="AB3" s="15"/>
-      <c r="AC3" s="15"/>
-      <c r="AD3" s="15"/>
-      <c r="AE3" s="15"/>
-      <c r="AF3" s="15"/>
-      <c r="AG3" s="15"/>
-      <c r="AH3" s="15"/>
-      <c r="AI3" s="15"/>
-      <c r="AJ3" s="15"/>
-      <c r="AK3" s="15"/>
-      <c r="AL3" s="15"/>
-      <c r="AM3" s="15"/>
-      <c r="AN3" s="15"/>
-      <c r="AO3" s="15"/>
-      <c r="AP3" s="15"/>
-      <c r="AQ3" s="15"/>
-      <c r="AR3" s="15"/>
-      <c r="AS3" s="8"/>
-      <c r="AT3" s="8"/>
-      <c r="AU3" s="43"/>
-      <c r="AV3" s="43"/>
-      <c r="AW3" s="43"/>
-      <c r="AX3" s="43"/>
-      <c r="AY3" s="43"/>
-      <c r="AZ3" s="43"/>
-      <c r="BA3" s="43"/>
-      <c r="BB3" s="43"/>
-      <c r="BC3" s="43"/>
-      <c r="BD3" s="59"/>
-      <c r="BE3" s="8"/>
-      <c r="BF3" s="8"/>
+    <row r="3" ht="15.15" spans="1:58">
+      <c r="A3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="11"/>
+      <c r="T3" s="11"/>
+      <c r="U3" s="11"/>
+      <c r="V3" s="11"/>
+      <c r="W3" s="11"/>
+      <c r="X3" s="11"/>
+      <c r="Y3" s="11"/>
+      <c r="Z3" s="11"/>
+      <c r="AA3" s="11"/>
+      <c r="AB3" s="11"/>
+      <c r="AC3" s="11"/>
+      <c r="AD3" s="11"/>
+      <c r="AE3" s="11"/>
+      <c r="AF3" s="11"/>
+      <c r="AG3" s="11"/>
+      <c r="AH3" s="11"/>
+      <c r="AI3" s="11"/>
+      <c r="AJ3" s="11"/>
+      <c r="AK3" s="11"/>
+      <c r="AL3" s="11"/>
+      <c r="AM3" s="11"/>
+      <c r="AN3" s="11"/>
+      <c r="AO3" s="11"/>
+      <c r="AP3" s="11"/>
+      <c r="AQ3" s="11"/>
+      <c r="AR3" s="11"/>
+      <c r="AS3" s="5"/>
+      <c r="AT3" s="5"/>
+      <c r="AU3" s="35"/>
+      <c r="AV3" s="35"/>
+      <c r="AW3" s="35"/>
+      <c r="AX3" s="35"/>
+      <c r="AY3" s="35"/>
+      <c r="AZ3" s="35"/>
+      <c r="BA3" s="35"/>
+      <c r="BB3" s="35"/>
+      <c r="BC3" s="35"/>
+      <c r="BD3" s="51"/>
+      <c r="BE3" s="5"/>
+      <c r="BF3" s="5"/>
     </row>
     <row r="4" spans="1:58">
-      <c r="A4" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
-      <c r="S4" s="19"/>
-      <c r="T4" s="19"/>
-      <c r="U4" s="19"/>
-      <c r="V4" s="19"/>
-      <c r="W4" s="19"/>
-      <c r="X4" s="19"/>
-      <c r="Y4" s="19"/>
-      <c r="Z4" s="19"/>
-      <c r="AA4" s="19"/>
-      <c r="AB4" s="19"/>
-      <c r="AC4" s="19"/>
-      <c r="AD4" s="19"/>
-      <c r="AE4" s="19"/>
-      <c r="AF4" s="19"/>
-      <c r="AG4" s="19"/>
-      <c r="AH4" s="19"/>
-      <c r="AI4" s="19"/>
-      <c r="AJ4" s="19"/>
-      <c r="AK4" s="19"/>
-      <c r="AL4" s="19"/>
-      <c r="AM4" s="19"/>
-      <c r="AN4" s="19"/>
-      <c r="AO4" s="19"/>
-      <c r="AP4" s="19"/>
-      <c r="AQ4" s="19"/>
-      <c r="AR4" s="44"/>
-      <c r="AS4" s="44"/>
-      <c r="AT4" s="45"/>
-      <c r="AU4" s="46" t="s">
+      <c r="A4" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="AV4" s="47"/>
-      <c r="AW4" s="47"/>
-      <c r="AX4" s="47"/>
-      <c r="AY4" s="47"/>
-      <c r="AZ4" s="47"/>
-      <c r="BA4" s="47"/>
-      <c r="BB4" s="47"/>
-      <c r="BC4" s="47"/>
-      <c r="BD4" s="60"/>
-      <c r="BE4" s="72" t="s">
+      <c r="B4" s="13"/>
+      <c r="C4" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="BF4" s="73" t="s">
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="15"/>
+      <c r="U4" s="15"/>
+      <c r="V4" s="15"/>
+      <c r="W4" s="15"/>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="15"/>
+      <c r="Z4" s="15"/>
+      <c r="AA4" s="15"/>
+      <c r="AB4" s="15"/>
+      <c r="AC4" s="15"/>
+      <c r="AD4" s="15"/>
+      <c r="AE4" s="15"/>
+      <c r="AF4" s="15"/>
+      <c r="AG4" s="15"/>
+      <c r="AH4" s="15"/>
+      <c r="AI4" s="15"/>
+      <c r="AJ4" s="15"/>
+      <c r="AK4" s="15"/>
+      <c r="AL4" s="15"/>
+      <c r="AM4" s="15"/>
+      <c r="AN4" s="15"/>
+      <c r="AO4" s="15"/>
+      <c r="AP4" s="15"/>
+      <c r="AQ4" s="15"/>
+      <c r="AR4" s="36"/>
+      <c r="AS4" s="36"/>
+      <c r="AT4" s="37"/>
+      <c r="AU4" s="38" t="s">
         <v>16</v>
       </c>
+      <c r="AV4" s="39"/>
+      <c r="AW4" s="39"/>
+      <c r="AX4" s="39"/>
+      <c r="AY4" s="39"/>
+      <c r="AZ4" s="39"/>
+      <c r="BA4" s="39"/>
+      <c r="BB4" s="39"/>
+      <c r="BC4" s="39"/>
+      <c r="BD4" s="52"/>
+      <c r="BE4" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="BF4" s="65" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="5" ht="67.5" spans="1:58">
-      <c r="A5" s="20"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="24" t="s">
+    <row r="5" ht="64.8" spans="1:58">
+      <c r="A5" s="16"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="24" t="s">
+      <c r="E5" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="24" t="s">
+      <c r="F5" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="24" t="s">
+      <c r="G5" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="24" t="s">
+      <c r="H5" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="K5" s="24" t="s">
+      <c r="I5" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="L5" s="24" t="s">
+      <c r="J5" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="24" t="s">
+      <c r="K5" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="24" t="s">
+      <c r="L5" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="O5" s="24" t="s">
+      <c r="M5" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="P5" s="24" t="s">
+      <c r="N5" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="Q5" s="39" t="s">
+      <c r="O5" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="R5" s="39" t="s">
+      <c r="P5" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="S5" s="39" t="s">
+      <c r="Q5" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="T5" s="39" t="s">
+      <c r="R5" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="U5" s="40" t="s">
+      <c r="S5" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="V5" s="39" t="s">
+      <c r="T5" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="W5" s="39" t="s">
+      <c r="U5" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="X5" s="39" t="s">
+      <c r="V5" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="Y5" s="39" t="s">
+      <c r="W5" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="Z5" s="40" t="s">
+      <c r="X5" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="AA5" s="40" t="s">
+      <c r="Y5" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="AB5" s="40" t="s">
+      <c r="Z5" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="AC5" s="40" t="s">
+      <c r="AA5" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="AD5" s="39" t="s">
+      <c r="AB5" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="AE5" s="39" t="s">
+      <c r="AC5" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="AF5" s="39" t="s">
+      <c r="AD5" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="AG5" s="39" t="s">
+      <c r="AE5" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="AH5" s="39" t="s">
+      <c r="AF5" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="AI5" s="39" t="s">
+      <c r="AG5" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="AJ5" s="39" t="s">
+      <c r="AH5" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="AK5" s="39" t="s">
+      <c r="AI5" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="AL5" s="39" t="s">
+      <c r="AJ5" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="AM5" s="39" t="s">
+      <c r="AK5" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="AN5" s="39" t="s">
+      <c r="AL5" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="AO5" s="39" t="s">
+      <c r="AM5" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="AP5" s="39" t="s">
+      <c r="AN5" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="AQ5" s="39" t="s">
+      <c r="AO5" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="AR5" s="39" t="s">
+      <c r="AP5" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="AS5" s="39" t="s">
+      <c r="AQ5" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="AT5" s="48" t="s">
+      <c r="AR5" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="AU5" s="49" t="s">
+      <c r="AS5" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="AV5" s="49" t="s">
+      <c r="AT5" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="AW5" s="61" t="s">
+      <c r="AU5" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="AX5" s="49" t="s">
+      <c r="AV5" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="AY5" s="61" t="s">
+      <c r="AW5" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="AZ5" s="49" t="s">
+      <c r="AX5" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="BA5" s="49" t="s">
+      <c r="AY5" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="BB5" s="61" t="s">
+      <c r="AZ5" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="BC5" s="62" t="s">
+      <c r="BA5" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="BD5" s="63" t="s">
+      <c r="BB5" s="53" t="s">
         <v>69</v>
       </c>
-      <c r="BE5" s="74"/>
-      <c r="BF5" s="75"/>
+      <c r="BC5" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="BD5" s="55" t="s">
+        <v>71</v>
+      </c>
+      <c r="BE5" s="66"/>
+      <c r="BF5" s="67"/>
     </row>
     <row r="6" spans="1:58">
-      <c r="A6" s="25"/>
-      <c r="B6" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" s="28" t="s">
+      <c r="A6" s="5"/>
+      <c r="B6" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="F6" s="29" t="s">
+      <c r="D6" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="G6" s="28" t="s">
+      <c r="E6" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="H6" s="28" t="s">
+      <c r="F6" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="I6" s="28" t="s">
+      <c r="G6" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="J6" s="28" t="s">
+      <c r="H6" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="K6" s="28" t="s">
+      <c r="I6" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="L6" s="28" t="s">
+      <c r="J6" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="M6" s="28" t="s">
+      <c r="K6" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="N6" s="28" t="s">
+      <c r="L6" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="O6" s="28" t="s">
+      <c r="M6" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="P6" s="28" t="s">
+      <c r="N6" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="Q6" s="28" t="s">
+      <c r="O6" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="R6" s="28" t="s">
+      <c r="P6" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="S6" s="28" t="s">
+      <c r="Q6" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="T6" s="28" t="s">
+      <c r="R6" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="U6" s="28" t="s">
+      <c r="S6" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="V6" s="28" t="s">
+      <c r="T6" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="W6" s="28" t="s">
+      <c r="U6" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="X6" s="28" t="s">
+      <c r="V6" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="Y6" s="28" t="s">
+      <c r="W6" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="Z6" s="28" t="s">
+      <c r="X6" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="AA6" s="28" t="s">
+      <c r="Y6" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="AB6" s="28" t="s">
+      <c r="Z6" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="AC6" s="28" t="s">
+      <c r="AA6" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="AD6" s="28" t="s">
+      <c r="AB6" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="AE6" s="28" t="s">
+      <c r="AC6" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="AF6" s="28" t="s">
+      <c r="AD6" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="AG6" s="28" t="s">
+      <c r="AE6" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="AH6" s="28" t="s">
+      <c r="AF6" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="AI6" s="28" t="s">
+      <c r="AG6" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="AJ6" s="28" t="s">
+      <c r="AH6" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="AK6" s="28" t="s">
+      <c r="AI6" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="AL6" s="28" t="s">
+      <c r="AJ6" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="AM6" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="AN6" s="28" t="s">
+      <c r="AK6" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="AO6" s="28" t="s">
+      <c r="AL6" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="AP6" s="28" t="s">
+      <c r="AM6" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="AQ6" s="28" t="s">
+      <c r="AN6" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="AR6" s="28" t="s">
+      <c r="AO6" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="AS6" s="28" t="s">
+      <c r="AP6" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="AT6" s="28" t="s">
+      <c r="AQ6" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="AU6" s="50" t="s">
+      <c r="AR6" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="AV6" s="50" t="s">
+      <c r="AS6" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="AW6" s="64" t="s">
+      <c r="AT6" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="AX6" s="50" t="s">
+      <c r="AU6" s="42" t="s">
         <v>116</v>
       </c>
-      <c r="AY6" s="64" t="s">
+      <c r="AV6" s="42" t="s">
         <v>117</v>
       </c>
-      <c r="AZ6" s="50" t="s">
+      <c r="AW6" s="56" t="s">
         <v>118</v>
       </c>
-      <c r="BA6" s="50" t="s">
+      <c r="AX6" s="42" t="s">
         <v>119</v>
       </c>
-      <c r="BB6" s="64" t="s">
+      <c r="AY6" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="BC6" s="65" t="s">
+      <c r="AZ6" s="42" t="s">
         <v>121</v>
       </c>
-      <c r="BD6" s="66" t="s">
+      <c r="BA6" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="BE6" s="76" t="s">
+      <c r="BB6" s="56" t="s">
         <v>123</v>
       </c>
-      <c r="BF6" s="77" t="s">
+      <c r="BC6" s="57" t="s">
         <v>124</v>
+      </c>
+      <c r="BD6" s="58" t="s">
+        <v>125</v>
+      </c>
+      <c r="BE6" s="68" t="s">
+        <v>126</v>
+      </c>
+      <c r="BF6" s="69" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:58">
-      <c r="A7" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>127</v>
-      </c>
-      <c r="D7" s="33">
+      <c r="A7" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="D7" s="27">
         <v>821109376.632051</v>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="27">
         <v>49156975.9562107</v>
       </c>
-      <c r="F7" s="33">
+      <c r="F7" s="27">
         <v>10684586.8078278</v>
       </c>
-      <c r="G7" s="33">
+      <c r="G7" s="27">
         <v>34146732.2608017</v>
       </c>
-      <c r="H7" s="33">
+      <c r="H7" s="27">
         <v>9070894.78577535</v>
       </c>
-      <c r="I7" s="33">
+      <c r="I7" s="27">
         <v>92288059.9056758</v>
       </c>
-      <c r="J7" s="33">
+      <c r="J7" s="27">
         <v>78070178.6100447</v>
       </c>
-      <c r="K7" s="33">
+      <c r="K7" s="27">
         <v>25339700.6887769</v>
       </c>
-      <c r="L7" s="33">
+      <c r="L7" s="27">
         <v>70607744.9636081</v>
       </c>
-      <c r="M7" s="33">
+      <c r="M7" s="27">
         <v>12815275.3213411</v>
       </c>
-      <c r="N7" s="33">
+      <c r="N7" s="27">
         <v>47509590.2427704</v>
       </c>
-      <c r="O7" s="33">
+      <c r="O7" s="27">
         <v>30588660.7146926</v>
       </c>
-      <c r="P7" s="33">
+      <c r="P7" s="27">
         <v>35944267.4865012</v>
       </c>
-      <c r="Q7" s="33">
+      <c r="Q7" s="27">
         <v>74959951.9783755</v>
       </c>
-      <c r="R7" s="33">
+      <c r="R7" s="27">
         <v>39116758.5176721</v>
       </c>
-      <c r="S7" s="33">
+      <c r="S7" s="27">
         <v>35418933.9930419</v>
       </c>
-      <c r="T7" s="33">
+      <c r="T7" s="27">
         <v>57488356.1501572</v>
       </c>
-      <c r="U7" s="33">
+      <c r="U7" s="27">
         <v>46988959.7259126</v>
       </c>
-      <c r="V7" s="33">
+      <c r="V7" s="27">
         <v>51031136.4146658</v>
       </c>
-      <c r="W7" s="33">
+      <c r="W7" s="27">
         <v>36758514.0184566</v>
       </c>
-      <c r="X7" s="33">
+      <c r="X7" s="27">
         <v>17700419.3798486</v>
       </c>
-      <c r="Y7" s="33">
+      <c r="Y7" s="27">
         <v>47111753.5845014</v>
       </c>
-      <c r="Z7" s="33">
+      <c r="Z7" s="27">
         <v>100330129.042527</v>
       </c>
-      <c r="AA7" s="33">
+      <c r="AA7" s="27">
         <v>25541967.5256686</v>
       </c>
-      <c r="AB7" s="33">
+      <c r="AB7" s="27">
         <v>61395231.1624101</v>
       </c>
-      <c r="AC7" s="33">
+      <c r="AC7" s="27">
         <v>7256304.22228311</v>
       </c>
-      <c r="AD7" s="33">
+      <c r="AD7" s="27">
         <v>8632889.79187755</v>
       </c>
-      <c r="AE7" s="33">
+      <c r="AE7" s="27">
         <v>469645429.010662</v>
       </c>
-      <c r="AF7" s="33">
+      <c r="AF7" s="27">
         <v>519792503.263792</v>
       </c>
-      <c r="AG7" s="33">
+      <c r="AG7" s="27">
         <v>230523925.740211</v>
       </c>
-      <c r="AH7" s="33">
+      <c r="AH7" s="27">
         <v>85067117.1008988</v>
       </c>
-      <c r="AI7" s="33">
+      <c r="AI7" s="27">
         <v>206973736.679317</v>
       </c>
-      <c r="AJ7" s="33">
+      <c r="AJ7" s="27">
         <v>215281976.520711</v>
       </c>
-      <c r="AK7" s="33">
+      <c r="AK7" s="27">
         <v>192733122.55735</v>
       </c>
-      <c r="AL7" s="33">
+      <c r="AL7" s="27">
         <v>252757212.793925</v>
       </c>
-      <c r="AM7" s="33">
+      <c r="AM7" s="27">
         <v>65841576.822612</v>
       </c>
-      <c r="AN7" s="33">
+      <c r="AN7" s="27">
         <v>115418456.212316</v>
       </c>
-      <c r="AO7" s="33">
+      <c r="AO7" s="27">
         <v>127689767.858012</v>
       </c>
-      <c r="AP7" s="33">
+      <c r="AP7" s="27">
         <v>281650493.11452</v>
       </c>
-      <c r="AQ7" s="33">
+      <c r="AQ7" s="27">
         <v>171783188.525367</v>
       </c>
-      <c r="AR7" s="33">
+      <c r="AR7" s="27">
         <v>51172539.734951</v>
       </c>
-      <c r="AS7" s="33">
+      <c r="AS7" s="27">
         <v>407600705.014876</v>
       </c>
-      <c r="AT7" s="51">
+      <c r="AT7" s="43">
         <v>5295655400.14422</v>
       </c>
-      <c r="AU7" s="52"/>
-      <c r="AV7" s="52"/>
-      <c r="AW7" s="67"/>
-      <c r="AX7" s="52"/>
-      <c r="AY7" s="67"/>
-      <c r="AZ7" s="52"/>
-      <c r="BA7" s="52"/>
-      <c r="BB7" s="67"/>
-      <c r="BC7" s="52"/>
-      <c r="BD7" s="68"/>
-      <c r="BE7" s="52"/>
-      <c r="BF7" s="52"/>
+      <c r="AU7" s="44"/>
+      <c r="AV7" s="44"/>
+      <c r="AW7" s="59"/>
+      <c r="AX7" s="44"/>
+      <c r="AY7" s="59"/>
+      <c r="AZ7" s="44"/>
+      <c r="BA7" s="44"/>
+      <c r="BB7" s="59"/>
+      <c r="BC7" s="44"/>
+      <c r="BD7" s="60"/>
+      <c r="BE7" s="44"/>
+      <c r="BF7" s="44"/>
     </row>
     <row r="8" spans="1:58">
-      <c r="A8" s="34"/>
-      <c r="B8" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="C8" s="35" t="s">
-        <v>129</v>
-      </c>
-      <c r="D8" s="33">
+      <c r="A8" s="28"/>
+      <c r="B8" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" s="27">
         <v>-45528240.6524828</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="27">
         <v>23728883.970035</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="27">
         <v>26393586.367127</v>
       </c>
-      <c r="G8" s="33">
+      <c r="G8" s="27">
         <v>29203561.314</v>
       </c>
-      <c r="H8" s="33">
+      <c r="H8" s="27">
         <v>1127941.29772883</v>
       </c>
-      <c r="I8" s="33">
+      <c r="I8" s="27">
         <v>82927929.5671502</v>
       </c>
-      <c r="J8" s="33">
+      <c r="J8" s="27">
         <v>1055456.5261335</v>
       </c>
-      <c r="K8" s="33">
+      <c r="K8" s="27">
         <v>5439494.60237603</v>
       </c>
-      <c r="L8" s="33">
+      <c r="L8" s="27">
         <v>11735859.5567258</v>
       </c>
-      <c r="M8" s="33">
+      <c r="M8" s="27">
         <v>49155195.5214141</v>
       </c>
-      <c r="N8" s="33">
+      <c r="N8" s="27">
         <v>37768625.1294872</v>
       </c>
-      <c r="O8" s="33">
+      <c r="O8" s="27">
         <v>11543781.6746586</v>
       </c>
-      <c r="P8" s="33">
+      <c r="P8" s="27">
         <v>9432919.72683331</v>
       </c>
-      <c r="Q8" s="33">
+      <c r="Q8" s="27">
         <v>23472866.7779206</v>
       </c>
-      <c r="R8" s="33">
+      <c r="R8" s="27">
         <v>16809803.9852195</v>
       </c>
-      <c r="S8" s="33">
+      <c r="S8" s="27">
         <v>20103752.8548938</v>
       </c>
-      <c r="T8" s="33">
+      <c r="T8" s="27">
         <v>11219546.9861507</v>
       </c>
-      <c r="U8" s="33">
+      <c r="U8" s="27">
         <v>16723537.9683136</v>
       </c>
-      <c r="V8" s="33">
+      <c r="V8" s="27">
         <v>14548976.722464</v>
       </c>
-      <c r="W8" s="33">
+      <c r="W8" s="27">
         <v>41488605.881303</v>
       </c>
-      <c r="X8" s="33">
+      <c r="X8" s="27">
         <v>2028721.97909231</v>
       </c>
-      <c r="Y8" s="33">
+      <c r="Y8" s="27">
         <v>4541468.4707146</v>
       </c>
-      <c r="Z8" s="33">
+      <c r="Z8" s="27">
         <v>-3678836.27294552</v>
       </c>
-      <c r="AA8" s="33">
+      <c r="AA8" s="27">
         <v>13432368.4743476</v>
       </c>
-      <c r="AB8" s="33">
+      <c r="AB8" s="27">
         <v>20698377.6315251</v>
       </c>
-      <c r="AC8" s="33">
+      <c r="AC8" s="27">
         <v>1010550.45236413</v>
       </c>
-      <c r="AD8" s="33">
+      <c r="AD8" s="27">
         <v>1860447.18374642</v>
       </c>
-      <c r="AE8" s="33">
+      <c r="AE8" s="27">
         <v>98116385.5968287</v>
       </c>
-      <c r="AF8" s="33">
+      <c r="AF8" s="27">
         <v>95383190.2804768</v>
       </c>
-      <c r="AG8" s="33">
+      <c r="AG8" s="27">
         <v>8513567.44219846</v>
       </c>
-      <c r="AH8" s="33">
+      <c r="AH8" s="27">
         <v>1360038.66259777</v>
       </c>
-      <c r="AI8" s="33">
+      <c r="AI8" s="27">
         <v>13092894.4785477</v>
       </c>
-      <c r="AJ8" s="33">
+      <c r="AJ8" s="27">
         <v>82718115.8873387</v>
       </c>
-      <c r="AK8" s="33">
+      <c r="AK8" s="27">
         <v>123442718.311865</v>
       </c>
-      <c r="AL8" s="33">
+      <c r="AL8" s="27">
         <v>27690530.6917165</v>
       </c>
-      <c r="AM8" s="33">
+      <c r="AM8" s="27">
         <v>1588413.56834034</v>
       </c>
-      <c r="AN8" s="33">
+      <c r="AN8" s="27">
         <v>11715874.6086849</v>
       </c>
-      <c r="AO8" s="33">
+      <c r="AO8" s="27">
         <v>5023484.24607627</v>
       </c>
-      <c r="AP8" s="33">
+      <c r="AP8" s="27">
         <v>625840.589067589</v>
       </c>
-      <c r="AQ8" s="33">
+      <c r="AQ8" s="27">
         <v>119102.009382813</v>
       </c>
-      <c r="AR8" s="33">
+      <c r="AR8" s="27">
         <v>1590021.04931616</v>
       </c>
-      <c r="AS8" s="33">
+      <c r="AS8" s="27">
         <v>2016363.5215086</v>
       </c>
-      <c r="AT8" s="51">
+      <c r="AT8" s="43">
         <v>895802230.037866</v>
       </c>
-      <c r="AU8" s="53"/>
-      <c r="AV8" s="53"/>
-      <c r="AW8" s="69"/>
-      <c r="AX8" s="53"/>
-      <c r="AY8" s="69"/>
-      <c r="AZ8" s="53"/>
-      <c r="BA8" s="53"/>
-      <c r="BB8" s="69"/>
-      <c r="BC8" s="53"/>
-      <c r="BD8" s="70"/>
-      <c r="BE8" s="53"/>
-      <c r="BF8" s="53"/>
+      <c r="AU8" s="45"/>
+      <c r="AV8" s="45"/>
+      <c r="AW8" s="61"/>
+      <c r="AX8" s="45"/>
+      <c r="AY8" s="61"/>
+      <c r="AZ8" s="45"/>
+      <c r="BA8" s="45"/>
+      <c r="BB8" s="61"/>
+      <c r="BC8" s="45"/>
+      <c r="BD8" s="62"/>
+      <c r="BE8" s="45"/>
+      <c r="BF8" s="45"/>
     </row>
-    <row r="9" ht="22.5" spans="1:58">
-      <c r="A9" s="34"/>
-      <c r="B9" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="C9" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="D9" s="33">
+    <row r="9" ht="21.6" spans="1:58">
+      <c r="A9" s="28"/>
+      <c r="B9" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="D9" s="27">
         <v>23048579.7015093</v>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="27">
         <v>11857466.9359743</v>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="27">
         <v>23934531.6640675</v>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="27">
         <v>14045534.8444722</v>
       </c>
-      <c r="H9" s="33">
+      <c r="H9" s="27">
         <v>881427.489091594</v>
       </c>
-      <c r="I9" s="33">
+      <c r="I9" s="27">
         <v>30616039.4796629</v>
       </c>
-      <c r="J9" s="33">
+      <c r="J9" s="27">
         <v>17159912.3984095</v>
       </c>
-      <c r="K9" s="33">
+      <c r="K9" s="27">
         <v>7115541.18523375</v>
       </c>
-      <c r="L9" s="33">
+      <c r="L9" s="27">
         <v>23476685.1205348</v>
       </c>
-      <c r="M9" s="33">
+      <c r="M9" s="27">
         <v>11540322.9497796</v>
       </c>
-      <c r="N9" s="33">
+      <c r="N9" s="27">
         <v>37261752.7842075</v>
       </c>
-      <c r="O9" s="33">
+      <c r="O9" s="27">
         <v>7442373.45766556</v>
       </c>
-      <c r="P9" s="33">
+      <c r="P9" s="27">
         <v>13681348.1598697</v>
       </c>
-      <c r="Q9" s="33">
+      <c r="Q9" s="27">
         <v>36252424.8424867</v>
       </c>
-      <c r="R9" s="33">
+      <c r="R9" s="27">
         <v>31732255.9204724</v>
       </c>
-      <c r="S9" s="33">
+      <c r="S9" s="27">
         <v>20256127.1648298</v>
       </c>
-      <c r="T9" s="33">
+      <c r="T9" s="27">
         <v>17451919.7586117</v>
       </c>
-      <c r="U9" s="33">
+      <c r="U9" s="27">
         <v>16689439.146307</v>
       </c>
-      <c r="V9" s="33">
+      <c r="V9" s="27">
         <v>12133972.5831076</v>
       </c>
-      <c r="W9" s="33">
+      <c r="W9" s="27">
         <v>15404029.9075229</v>
       </c>
-      <c r="X9" s="33">
+      <c r="X9" s="27">
         <v>3816835.02801987</v>
       </c>
-      <c r="Y9" s="33">
+      <c r="Y9" s="27">
         <v>15983410.4130126</v>
       </c>
-      <c r="Z9" s="33">
+      <c r="Z9" s="27">
         <v>35286959.999098</v>
       </c>
-      <c r="AA9" s="33">
+      <c r="AA9" s="27">
         <v>6722131.42762518</v>
       </c>
-      <c r="AB9" s="33">
+      <c r="AB9" s="27">
         <v>97784316.3482651</v>
       </c>
-      <c r="AC9" s="33">
+      <c r="AC9" s="27">
         <v>5463403.96630397</v>
       </c>
-      <c r="AD9" s="33">
+      <c r="AD9" s="27">
         <v>6900167.08475439</v>
       </c>
-      <c r="AE9" s="33">
+      <c r="AE9" s="27">
         <v>27714363.6799584</v>
       </c>
-      <c r="AF9" s="33">
+      <c r="AF9" s="27">
         <v>118467134.625324</v>
       </c>
-      <c r="AG9" s="33">
+      <c r="AG9" s="27">
         <v>200221941.685502</v>
       </c>
-      <c r="AH9" s="33">
+      <c r="AH9" s="27">
         <v>46183808.0137878</v>
       </c>
-      <c r="AI9" s="33">
+      <c r="AI9" s="27">
         <v>126694176.647774</v>
       </c>
-      <c r="AJ9" s="33">
+      <c r="AJ9" s="27">
         <v>36197643.6232485</v>
       </c>
-      <c r="AK9" s="33">
+      <c r="AK9" s="27">
         <v>70284261.2451192</v>
       </c>
-      <c r="AL9" s="33">
+      <c r="AL9" s="27">
         <v>35220354.3225643</v>
       </c>
-      <c r="AM9" s="33">
+      <c r="AM9" s="27">
         <v>20894697.1076679</v>
       </c>
-      <c r="AN9" s="33">
+      <c r="AN9" s="27">
         <v>47257245.8232094</v>
       </c>
-      <c r="AO9" s="33">
+      <c r="AO9" s="27">
         <v>18811000.5847299</v>
       </c>
-      <c r="AP9" s="33">
+      <c r="AP9" s="27">
         <v>77784703.2094327</v>
       </c>
-      <c r="AQ9" s="33">
+      <c r="AQ9" s="27">
         <v>31476065.1203941</v>
       </c>
-      <c r="AR9" s="33">
+      <c r="AR9" s="27">
         <v>19443051.9030816</v>
       </c>
-      <c r="AS9" s="33">
+      <c r="AS9" s="27">
         <v>92345943.1037209</v>
       </c>
-      <c r="AT9" s="51">
+      <c r="AT9" s="43">
         <v>1505819759.27118</v>
       </c>
-      <c r="AU9" s="53"/>
-      <c r="AV9" s="53"/>
-      <c r="AW9" s="69"/>
-      <c r="AX9" s="53"/>
-      <c r="AY9" s="69"/>
-      <c r="AZ9" s="53"/>
-      <c r="BA9" s="53"/>
-      <c r="BB9" s="69"/>
-      <c r="BC9" s="53"/>
-      <c r="BD9" s="71"/>
-      <c r="BE9" s="53"/>
-      <c r="BF9" s="53"/>
+      <c r="AU9" s="45"/>
+      <c r="AV9" s="45"/>
+      <c r="AW9" s="61"/>
+      <c r="AX9" s="45"/>
+      <c r="AY9" s="61"/>
+      <c r="AZ9" s="45"/>
+      <c r="BA9" s="45"/>
+      <c r="BB9" s="61"/>
+      <c r="BC9" s="45"/>
+      <c r="BD9" s="63"/>
+      <c r="BE9" s="45"/>
+      <c r="BF9" s="45"/>
     </row>
     <row r="10" spans="1:58">
-      <c r="A10" s="34"/>
-      <c r="B10" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="D10" s="33">
+      <c r="A10" s="28"/>
+      <c r="B10" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="D10" s="27">
         <v>23117526.7569887</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="27">
         <v>35255170.9583124</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="27">
         <v>6711085.03132599</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10" s="27">
         <v>26913764.7283137</v>
       </c>
-      <c r="H10" s="33">
+      <c r="H10" s="27">
         <v>-2541340.49459825</v>
       </c>
-      <c r="I10" s="33">
+      <c r="I10" s="27">
         <v>101181657.170058</v>
       </c>
-      <c r="J10" s="33">
+      <c r="J10" s="27">
         <v>48190809.1034635</v>
       </c>
-      <c r="K10" s="33">
+      <c r="K10" s="27">
         <v>17706881.846518</v>
       </c>
-      <c r="L10" s="33">
+      <c r="L10" s="27">
         <v>55330296.5377042</v>
       </c>
-      <c r="M10" s="33">
+      <c r="M10" s="27">
         <v>27079970.6715743</v>
       </c>
-      <c r="N10" s="33">
+      <c r="N10" s="27">
         <v>75473750.7006667</v>
       </c>
-      <c r="O10" s="33">
+      <c r="O10" s="27">
         <v>36261214.2131177</v>
       </c>
-      <c r="P10" s="33">
+      <c r="P10" s="27">
         <v>27380721.776729</v>
       </c>
-      <c r="Q10" s="33">
+      <c r="Q10" s="27">
         <v>95894757.611015</v>
       </c>
-      <c r="R10" s="33">
+      <c r="R10" s="27">
         <v>68635495.4348648</v>
       </c>
-      <c r="S10" s="33">
+      <c r="S10" s="27">
         <v>43798631.4097935</v>
       </c>
-      <c r="T10" s="33">
+      <c r="T10" s="27">
         <v>41037939.5122591</v>
       </c>
-      <c r="U10" s="33">
+      <c r="U10" s="27">
         <v>43686015.7589667</v>
       </c>
-      <c r="V10" s="33">
+      <c r="V10" s="27">
         <v>20237210.5040328</v>
       </c>
-      <c r="W10" s="33">
+      <c r="W10" s="27">
         <v>51825291.1612023</v>
       </c>
-      <c r="X10" s="33">
+      <c r="X10" s="27">
         <v>8695606.88428179</v>
       </c>
-      <c r="Y10" s="33">
+      <c r="Y10" s="27">
         <v>53690205.7608763</v>
       </c>
-      <c r="Z10" s="33">
+      <c r="Z10" s="27">
         <v>59374527.4317411</v>
       </c>
-      <c r="AA10" s="33">
+      <c r="AA10" s="27">
         <v>51110402.0784249</v>
       </c>
-      <c r="AB10" s="33">
+      <c r="AB10" s="27">
         <v>38471081.0886827</v>
       </c>
-      <c r="AC10" s="33">
+      <c r="AC10" s="27">
         <v>5841588.01525428</v>
       </c>
-      <c r="AD10" s="33">
+      <c r="AD10" s="27">
         <v>3105561.83173584</v>
       </c>
-      <c r="AE10" s="33">
+      <c r="AE10" s="27">
         <v>124616761.457381</v>
       </c>
-      <c r="AF10" s="33">
+      <c r="AF10" s="27">
         <v>219960586.719413</v>
       </c>
-      <c r="AG10" s="33">
+      <c r="AG10" s="27">
         <v>17515502.0570903</v>
       </c>
-      <c r="AH10" s="33">
+      <c r="AH10" s="27">
         <v>12909619.8106462</v>
       </c>
-      <c r="AI10" s="33">
+      <c r="AI10" s="27">
         <v>101253636.088194</v>
       </c>
-      <c r="AJ10" s="33">
+      <c r="AJ10" s="27">
         <v>501973655.097806</v>
       </c>
-      <c r="AK10" s="33">
+      <c r="AK10" s="27">
         <v>383207440.021522</v>
       </c>
-      <c r="AL10" s="33">
+      <c r="AL10" s="27">
         <v>2859006.25501044</v>
       </c>
-      <c r="AM10" s="33">
+      <c r="AM10" s="27">
         <v>7602478.69404698</v>
       </c>
-      <c r="AN10" s="33">
+      <c r="AN10" s="27">
         <v>10750979.3816108</v>
       </c>
-      <c r="AO10" s="33">
+      <c r="AO10" s="27">
         <v>5752421.84212641</v>
       </c>
-      <c r="AP10" s="33">
+      <c r="AP10" s="27">
         <v>13231125.5114678</v>
       </c>
-      <c r="AQ10" s="33">
+      <c r="AQ10" s="27">
         <v>4827324.60917299</v>
       </c>
-      <c r="AR10" s="33">
+      <c r="AR10" s="27">
         <v>5804782.04253919</v>
       </c>
-      <c r="AS10" s="33">
+      <c r="AS10" s="27">
         <v>8918361.97051482</v>
       </c>
-      <c r="AT10" s="51">
+      <c r="AT10" s="43">
         <v>2466942623.19533</v>
       </c>
-      <c r="AU10" s="53"/>
-      <c r="AV10" s="53"/>
-      <c r="AW10" s="69"/>
-      <c r="AX10" s="53"/>
-      <c r="AY10" s="69"/>
-      <c r="AZ10" s="53"/>
-      <c r="BA10" s="53"/>
-      <c r="BB10" s="69"/>
-      <c r="BC10" s="53"/>
-      <c r="BD10" s="71"/>
-      <c r="BE10" s="53"/>
-      <c r="BF10" s="53"/>
+      <c r="AU10" s="45"/>
+      <c r="AV10" s="45"/>
+      <c r="AW10" s="61"/>
+      <c r="AX10" s="45"/>
+      <c r="AY10" s="61"/>
+      <c r="AZ10" s="45"/>
+      <c r="BA10" s="45"/>
+      <c r="BB10" s="61"/>
+      <c r="BC10" s="45"/>
+      <c r="BD10" s="63"/>
+      <c r="BE10" s="45"/>
+      <c r="BF10" s="45"/>
     </row>
-    <row r="11" spans="1:58">
-      <c r="A11" s="34"/>
-      <c r="B11" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="C11" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="D11" s="33">
+    <row r="11" ht="21.6" spans="1:58">
+      <c r="A11" s="28"/>
+      <c r="B11" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="D11" s="27">
         <v>821747242.438066</v>
       </c>
-      <c r="E11" s="38">
+      <c r="E11" s="32">
         <v>119998497.820532</v>
       </c>
-      <c r="F11" s="38">
+      <c r="F11" s="32">
         <v>67723789.8703483</v>
       </c>
-      <c r="G11" s="33">
+      <c r="G11" s="27">
         <v>104309593.147588</v>
       </c>
-      <c r="H11" s="38">
+      <c r="H11" s="32">
         <v>8538923.07799753</v>
       </c>
-      <c r="I11" s="33">
+      <c r="I11" s="27">
         <v>307013686.122547</v>
       </c>
-      <c r="J11" s="33">
+      <c r="J11" s="27">
         <v>144476356.638051</v>
       </c>
-      <c r="K11" s="33">
+      <c r="K11" s="27">
         <v>55601618.3229046</v>
       </c>
-      <c r="L11" s="33">
+      <c r="L11" s="27">
         <v>161150586.178573</v>
       </c>
-      <c r="M11" s="33">
+      <c r="M11" s="27">
         <v>100590764.464109</v>
       </c>
-      <c r="N11" s="33">
+      <c r="N11" s="27">
         <v>198013718.857132</v>
       </c>
-      <c r="O11" s="38">
+      <c r="O11" s="32">
         <v>85836030.0601345</v>
       </c>
-      <c r="P11" s="33">
+      <c r="P11" s="27">
         <v>86439257.1499332</v>
       </c>
-      <c r="Q11" s="33">
+      <c r="Q11" s="27">
         <v>230580001.209798</v>
       </c>
-      <c r="R11" s="33">
+      <c r="R11" s="27">
         <v>156294313.858229</v>
       </c>
-      <c r="S11" s="33">
+      <c r="S11" s="27">
         <v>119577445.422559</v>
       </c>
-      <c r="T11" s="38">
+      <c r="T11" s="32">
         <v>127197762.407179</v>
       </c>
-      <c r="U11" s="33">
+      <c r="U11" s="27">
         <v>124087952.5995</v>
       </c>
-      <c r="V11" s="33">
+      <c r="V11" s="27">
         <v>97951296.2242703</v>
       </c>
-      <c r="W11" s="33">
+      <c r="W11" s="27">
         <v>145476440.968485</v>
       </c>
-      <c r="X11" s="33">
+      <c r="X11" s="27">
         <v>32241583.2712426</v>
       </c>
-      <c r="Y11" s="33">
+      <c r="Y11" s="27">
         <v>121326838.229105</v>
       </c>
-      <c r="Z11" s="33">
+      <c r="Z11" s="27">
         <v>191312780.20042</v>
       </c>
-      <c r="AA11" s="33">
+      <c r="AA11" s="27">
         <v>96806869.5060662</v>
       </c>
-      <c r="AB11" s="38">
+      <c r="AB11" s="32">
         <v>218349006.230883</v>
       </c>
-      <c r="AC11" s="38">
+      <c r="AC11" s="32">
         <v>19571846.6562055</v>
       </c>
-      <c r="AD11" s="38">
+      <c r="AD11" s="32">
         <v>20499065.8921142</v>
       </c>
-      <c r="AE11" s="33">
+      <c r="AE11" s="27">
         <v>720092939.74483</v>
       </c>
-      <c r="AF11" s="33">
+      <c r="AF11" s="27">
         <v>953603414.889006</v>
       </c>
-      <c r="AG11" s="33">
+      <c r="AG11" s="27">
         <v>456774936.925002</v>
       </c>
-      <c r="AH11" s="33">
+      <c r="AH11" s="27">
         <v>145520583.587931</v>
       </c>
-      <c r="AI11" s="33">
+      <c r="AI11" s="27">
         <v>448014443.893833</v>
       </c>
-      <c r="AJ11" s="33">
+      <c r="AJ11" s="27">
         <v>836171391.129104</v>
       </c>
-      <c r="AK11" s="38">
+      <c r="AK11" s="32">
         <v>769667542.135856</v>
       </c>
-      <c r="AL11" s="33">
+      <c r="AL11" s="27">
         <v>318527104.063217</v>
       </c>
-      <c r="AM11" s="38">
+      <c r="AM11" s="32">
         <v>95927166.1926672</v>
       </c>
-      <c r="AN11" s="33">
+      <c r="AN11" s="27">
         <v>185142556.025821</v>
       </c>
-      <c r="AO11" s="33">
+      <c r="AO11" s="27">
         <v>157276674.530945</v>
       </c>
-      <c r="AP11" s="38">
+      <c r="AP11" s="32">
         <v>373292162.424488</v>
       </c>
-      <c r="AQ11" s="33">
+      <c r="AQ11" s="27">
         <v>208205680.264317</v>
       </c>
-      <c r="AR11" s="33">
+      <c r="AR11" s="27">
         <v>78010394.729888</v>
       </c>
-      <c r="AS11" s="33">
+      <c r="AS11" s="27">
         <v>510881373.61062</v>
       </c>
-      <c r="AT11" s="51">
+      <c r="AT11" s="43">
         <v>10164220012.6486</v>
       </c>
-      <c r="AU11" s="54"/>
-      <c r="AV11" s="53"/>
-      <c r="AW11" s="69"/>
-      <c r="AX11" s="53"/>
-      <c r="AY11" s="69"/>
-      <c r="AZ11" s="53"/>
-      <c r="BA11" s="53"/>
-      <c r="BB11" s="69"/>
-      <c r="BC11" s="53"/>
-      <c r="BD11" s="71"/>
-      <c r="BE11" s="53"/>
-      <c r="BF11" s="53"/>
+      <c r="AU11" s="46"/>
+      <c r="AV11" s="45"/>
+      <c r="AW11" s="61"/>
+      <c r="AX11" s="45"/>
+      <c r="AY11" s="61"/>
+      <c r="AZ11" s="45"/>
+      <c r="BA11" s="45"/>
+      <c r="BB11" s="61"/>
+      <c r="BC11" s="45"/>
+      <c r="BD11" s="63"/>
+      <c r="BE11" s="45"/>
+      <c r="BF11" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3445,448 +3543,324 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:AQ3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <sheetPr>
+    <tabColor theme="8" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1"/>
   <cols>
-    <col min="2" max="26" width="12.625"/>
+    <col min="1" max="2" width="12.8888888888889"/>
+    <col min="3" max="14" width="12.6296296296296"/>
+    <col min="15" max="16" width="12.8888888888889"/>
+    <col min="17" max="26" width="12.6296296296296"/>
     <col min="27" max="27" width="11.5"/>
-    <col min="28" max="28" width="12.625"/>
+    <col min="28" max="28" width="12.6296296296296"/>
     <col min="29" max="29" width="11.5"/>
-    <col min="30" max="43" width="12.625"/>
+    <col min="30" max="43" width="12.6296296296296"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="P1" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="S1" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="Q1" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="T1" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="X1" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="U1" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="Y1" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Z1" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AA1" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AC1" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AD1" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AE1" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AF1" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG1" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AH1" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AI1" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="AJ1" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="AK1" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AL1" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="AM1" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AN1" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="AN1" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="AO1" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AP1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="AQ1" s="2" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:43">
       <c r="A2" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B2">
-        <f>'2020年全国投入产出表'!$D$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$D$7*10000*About!$A$13</f>
         <v>1130262623958.98</v>
       </c>
       <c r="C2">
-        <f>'2020年全国投入产出表'!$E$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$E$7*10000*About!$A$13</f>
         <v>67664910682.2372</v>
       </c>
       <c r="D2">
-        <f>'2020年全国投入产出表'!$F$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$F$7*10000*About!$A$13</f>
         <v>14707406181.2164</v>
       </c>
       <c r="E2">
-        <f>'2020年全国投入产出表'!$G$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$G$7*10000*About!$A$13</f>
         <v>47003208467.8206</v>
       </c>
       <c r="F2">
-        <f>'2020年全国投入产出表'!$H$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$H$7*10000*About!$A$13</f>
         <v>12486148172.2191</v>
       </c>
       <c r="G2">
-        <f>'2020年全国投入产出表'!$I$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$I$7*10000*About!$A$13</f>
         <v>127035140162.35</v>
       </c>
       <c r="H2">
-        <f>'2020年全国投入产出表'!$J$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$J$7*10000*About!$A$13</f>
         <v>107464130163.352</v>
       </c>
       <c r="I2">
-        <f>'2020年全国投入产出表'!$K$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$K$7*10000*About!$A$13</f>
         <v>34880269798.2906</v>
       </c>
       <c r="J2">
-        <f>'2020年全国投入产出表'!$L$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$L$7*10000*About!$A$13</f>
         <v>97192039654.6097</v>
       </c>
       <c r="K2">
-        <f>'2020年全国投入产出表'!$M$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$M$7*10000*About!$A$13</f>
         <v>17640313365.8849</v>
       </c>
       <c r="L2">
-        <f>'2020年全国投入产出表'!$N$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$N$7*10000*About!$A$13</f>
         <v>65397273078.6053</v>
       </c>
       <c r="M2">
-        <f>'2020年全国投入产出表'!$O$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$O$7*10000*About!$A$13</f>
         <v>42105498861.295</v>
       </c>
       <c r="N2">
-        <f>'2020年全国投入产出表'!$P$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$P$7*10000*About!$A$13</f>
         <v>49477527893.0733</v>
       </c>
       <c r="O2">
-        <f>'2020年全国投入产出表'!$Q$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$V$7*10000*About!$A$13</f>
+        <v>70244705259.888</v>
+      </c>
+      <c r="P2">
+        <f>'2020 National eps IO'!$Q$7*10000*About!$A$13</f>
         <v>103182882117.889</v>
       </c>
-      <c r="P2">
-        <f>'2020年全国投入产出表'!$V$7*10000*About!$A$36</f>
-        <v>70244705259.888</v>
-      </c>
       <c r="Q2">
-        <f>'2020年全国投入产出表'!$R$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$R$7*10000*About!$A$13</f>
         <v>53844483306.5959</v>
       </c>
       <c r="R2">
-        <f>'2020年全国投入产出表'!$S$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$S$7*10000*About!$A$13</f>
         <v>48754402777.6273</v>
       </c>
       <c r="S2">
-        <f>'2020年全国投入产出表'!$T$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$T$7*10000*About!$A$13</f>
         <v>79133112004.982</v>
       </c>
       <c r="T2">
-        <f>'2020年全国投入产出表'!$Z$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$Z$7*10000*About!$A$13</f>
         <v>138105102853.508</v>
       </c>
       <c r="U2">
-        <f>'2020年全国投入产出表'!$Y$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$Y$7*10000*About!$A$13</f>
         <v>64849648221.2123</v>
       </c>
       <c r="V2">
-        <f>'2020年全国投入产出表'!$U$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$U$7*10000*About!$A$13</f>
         <v>64680621642.3369</v>
       </c>
       <c r="W2">
-        <f>'2020年全国投入产出表'!$W$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$W$7*10000*About!$A$13</f>
         <v>50598343764.8055</v>
       </c>
       <c r="X2">
-        <f>'2020年全国投入产出表'!$X$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$X$7*10000*About!$A$13</f>
         <v>24364747283.1224</v>
       </c>
       <c r="Y2">
-        <f>'2020年全国投入产出表'!$AA$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$AA$7*10000*About!$A$13</f>
         <v>35158691470.6174</v>
       </c>
       <c r="Z2">
-        <f>'2020年全国投入产出表'!$AB$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$AB$7*10000*About!$A$13</f>
         <v>84510951947.501</v>
       </c>
       <c r="AA2">
-        <f>'2020年全国投入产出表'!$AC$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$AC$7*10000*About!$A$13</f>
         <v>9988351958.86155</v>
       </c>
       <c r="AB2">
-        <f>'2020年全国投入产出表'!$AD$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$AD$7*10000*About!$A$13</f>
         <v>11883231328.4965</v>
       </c>
       <c r="AC2">
-        <f>'2020年全国投入产出表'!$AE$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$AE$7*10000*About!$A$13</f>
         <v>646470117173.926</v>
       </c>
       <c r="AD2">
-        <f>'2020年全国投入产出表'!$AF$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$AF$7*10000*About!$A$13</f>
         <v>715497904874.623</v>
       </c>
       <c r="AE2">
-        <f>'2020年全国投入产出表'!$AG$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$AG$7*10000*About!$A$13</f>
         <v>317317746706.493</v>
       </c>
       <c r="AF2">
-        <f>'2020年全国投入产出表'!$AH$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$AH$7*10000*About!$A$13</f>
         <v>117095463434.432</v>
       </c>
       <c r="AG2">
-        <f>'2020年全国投入产出表'!$AI$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$AI$7*10000*About!$A$13</f>
         <v>284900751796.662</v>
       </c>
       <c r="AH2">
-        <f>'2020年全国投入产出表'!$AL$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$AL$7*10000*About!$A$13</f>
         <v>347922017075.001</v>
       </c>
       <c r="AI2">
-        <f>'2020年全国投入产出表'!$AM$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$AM$7*10000*About!$A$13</f>
         <v>90631376894.4693</v>
       </c>
       <c r="AJ2">
-        <f>'2020年全国投入产出表'!$AJ$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$AJ$7*10000*About!$A$13</f>
         <v>296337100267.229</v>
       </c>
       <c r="AK2">
-        <f>'2020年全国投入产出表'!$AK$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$AK$7*10000*About!$A$13</f>
         <v>265298449908.086</v>
       </c>
       <c r="AL2">
-        <f>'2020年全国投入产出表'!$AN$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$AN$7*10000*About!$A$13</f>
         <v>158874287499.806</v>
       </c>
       <c r="AM2">
-        <f>'2020年全国投入产出表'!$AS$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$AS$7*10000*About!$A$13</f>
         <v>561065133937.799</v>
       </c>
       <c r="AN2">
-        <f>'2020年全国投入产出表'!$AP$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$AP$7*10000*About!$A$13</f>
         <v>387693813329.341</v>
       </c>
       <c r="AO2">
-        <f>'2020年全国投入产出表'!$AQ$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$AQ$7*10000*About!$A$13</f>
         <v>236460723674.974</v>
       </c>
       <c r="AP2">
-        <f>'2020年全国投入产出表'!$AR$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$AR$7*10000*About!$A$13</f>
         <v>70439347888.9585</v>
       </c>
       <c r="AQ2">
-        <f>'2020年全国投入产出表'!$AO$7*10000*About!$A$36</f>
+        <f>'2020 National eps IO'!$AO$7*10000*About!$A$13</f>
         <v>175765831178.156</v>
-      </c>
-    </row>
-    <row r="3" ht="45" spans="1:43">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="X3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD3" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE3" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AH3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AI3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AJ3" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AK3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AL3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="AM3" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="AN3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="AO3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="AP3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AQ3" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
